--- a/static/format-upload/KAWI-import-selling-barge.xlsx
+++ b/static/format-upload/KAWI-import-selling-barge.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10727"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10824"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/meinardus/Desktop/import data/template/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/meinardus/Project/python/mines-project/backend/static/format-upload/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0689AE19-A4B3-2349-8314-FFCF2A1C6CC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2123B561-4FE5-DE43-9AA6-A765C5D32FFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="880" windowWidth="36000" windowHeight="20100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="import-data" sheetId="3" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'import-data'!$A$1:$X$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'import-data'!$A$1:$Y$3</definedName>
   </definedNames>
   <calcPr calcId="191029" calcMode="autoNoTable"/>
   <extLst>
@@ -367,7 +367,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
   <si>
     <t>date_barging_in</t>
   </si>
@@ -469,6 +469,9 @@
   </si>
   <si>
     <t>date_barging_load</t>
+  </si>
+  <si>
+    <t>direct</t>
   </si>
 </sst>
 </file>
@@ -574,7 +577,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -649,6 +652,34 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1" tint="0.34998626667073579"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="1" tint="0.34998626667073579"/>
+      </top>
+      <bottom style="thin">
+        <color theme="1" tint="0.34998626667073579"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -656,7 +687,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -691,25 +722,25 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -731,6 +762,18 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -751,10 +794,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1054,7 +1093,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X7"/>
+  <dimension ref="A1:Y7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16" style="6" bestFit="1" customWidth="1"/>
@@ -1077,16 +1116,17 @@
     <col min="18" max="18" width="9" style="6" customWidth="1"/>
     <col min="19" max="19" width="12.5" style="6" customWidth="1"/>
     <col min="20" max="20" width="18.5" style="6" customWidth="1"/>
-    <col min="21" max="21" width="12.1640625" style="6" customWidth="1"/>
-    <col min="22" max="22" width="8.1640625" style="6" customWidth="1"/>
-    <col min="23" max="23" width="12.1640625" style="6" customWidth="1"/>
-    <col min="24" max="24" width="12.5" style="4" customWidth="1"/>
-    <col min="25" max="25" width="11.5" style="4"/>
-    <col min="26" max="26" width="13" style="4" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="11.5" style="4"/>
+    <col min="21" max="21" width="8.33203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="12.1640625" style="6" customWidth="1"/>
+    <col min="23" max="23" width="8.1640625" style="6" customWidth="1"/>
+    <col min="24" max="24" width="12.1640625" style="6" customWidth="1"/>
+    <col min="25" max="25" width="12.5" style="4" customWidth="1"/>
+    <col min="26" max="26" width="11.5" style="4"/>
+    <col min="27" max="27" width="13" style="4" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="11.5" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="2" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:25" s="2" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -1147,16 +1187,19 @@
       <c r="T1" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="U1" s="23" t="s">
+      <c r="U1" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="V1" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="V1" s="23"/>
-      <c r="W1" s="23" t="s">
+      <c r="W1" s="23"/>
+      <c r="X1" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="X1" s="5"/>
+      <c r="Y1" s="5"/>
     </row>
-    <row r="2" spans="1:24" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:25" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="12">
         <v>45869</v>
       </c>
@@ -1206,11 +1249,11 @@
         <v>30.11</v>
       </c>
       <c r="Q2" s="22" t="str">
-        <f>U2</f>
+        <f>V2</f>
         <v>SL_01</v>
       </c>
       <c r="R2" s="16">
-        <f>W2</f>
+        <f>X2</f>
         <v>1</v>
       </c>
       <c r="S2" s="16" t="s">
@@ -1219,24 +1262,25 @@
       <c r="T2" s="12">
         <v>45873</v>
       </c>
-      <c r="U2" s="24" t="str">
+      <c r="U2" s="27"/>
+      <c r="V2" s="24" t="str">
         <f>"SL_" &amp; TEXT(INT((COUNTIF($O$2:O2,O2)-1)/100)+1,"00")</f>
         <v>SL_01</v>
       </c>
-      <c r="V2" s="25" t="str">
+      <c r="W2" s="25" t="str">
         <f>IF(COUNTIF($O$2:O2,O2)&gt;100,"CHECK",IF(COUNTIF($O$2:O2,O2)&lt;1,"CHECK","SL_"&amp;TEXT(INT((COUNTIF($O$2:O2,O2)-1)/100)+1,"00")))</f>
         <v>SL_01</v>
       </c>
-      <c r="W2" s="25">
-        <f>INT((COUNTIFS($O$2:O2,O2,$U$2:U2,U2)-1)/20)+1</f>
+      <c r="X2" s="25">
+        <f>INT((COUNTIFS($O$2:O2,O2,$V$2:V2,V2)-1)/20)+1</f>
         <v>1</v>
       </c>
-      <c r="X2" s="1" t="str">
-        <f>V2 &amp; "-INC_" &amp; TEXT(W2,"00")</f>
+      <c r="Y2" s="1" t="str">
+        <f>W2 &amp; "-INC_" &amp; TEXT(X2,"00")</f>
         <v>SL_01-INC_01</v>
       </c>
     </row>
-    <row r="3" spans="1:24" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:25" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="12"/>
       <c r="B3" s="12"/>
       <c r="C3" s="13"/>
@@ -1256,25 +1300,26 @@
       <c r="Q3" s="22"/>
       <c r="R3" s="16"/>
       <c r="S3" s="16"/>
-      <c r="T3" s="12"/>
-      <c r="U3" s="24" t="str">
+      <c r="T3" s="28"/>
+      <c r="U3" s="29"/>
+      <c r="V3" s="24" t="str">
         <f>"SL_" &amp; TEXT(INT((COUNTIF($O$2:O3,O3)-1)/100)+1,"00")</f>
         <v>SL_00</v>
       </c>
-      <c r="V3" s="25" t="str">
+      <c r="W3" s="25" t="str">
         <f>IF(COUNTIF($O$2:O3,O3)&gt;100,"CHECK",IF(COUNTIF($O$2:O3,O3)&lt;1,"CHECK","SL_"&amp;TEXT(INT((COUNTIF($O$2:O3,O3)-1)/100)+1,"00")))</f>
         <v>CHECK</v>
       </c>
-      <c r="W3" s="25">
-        <f>INT((COUNTIFS($O$2:O3,O3,$U$2:U3,U3)-1)/20)+1</f>
+      <c r="X3" s="25">
+        <f>INT((COUNTIFS($O$2:O3,O3,$V$2:V3,V3)-1)/20)+1</f>
         <v>0</v>
       </c>
-      <c r="X3" s="1" t="str">
-        <f t="shared" ref="X3" si="0">V3 &amp; "-INC_" &amp; TEXT(W3,"00")</f>
+      <c r="Y3" s="1" t="str">
+        <f t="shared" ref="Y3" si="0">W3 &amp; "-INC_" &amp; TEXT(X3,"00")</f>
         <v>CHECK-INC_00</v>
       </c>
     </row>
-    <row r="4" spans="1:24" ht="16" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" s="12"/>
       <c r="B4" s="12"/>
       <c r="C4" s="13"/>
@@ -1294,25 +1339,26 @@
       <c r="Q4" s="22"/>
       <c r="R4" s="16"/>
       <c r="S4" s="16"/>
-      <c r="T4" s="12"/>
-      <c r="U4" s="24" t="str">
+      <c r="T4" s="28"/>
+      <c r="U4" s="29"/>
+      <c r="V4" s="24" t="str">
         <f>"SL_" &amp; TEXT(INT((COUNTIF($O$2:O4,O4)-1)/100)+1,"00")</f>
         <v>SL_00</v>
       </c>
-      <c r="V4" s="25" t="str">
+      <c r="W4" s="25" t="str">
         <f>IF(COUNTIF($O$2:O4,O4)&gt;100,"CHECK",IF(COUNTIF($O$2:O4,O4)&lt;1,"CHECK","SL_"&amp;TEXT(INT((COUNTIF($O$2:O4,O4)-1)/100)+1,"00")))</f>
         <v>CHECK</v>
       </c>
-      <c r="W4" s="25">
-        <f>INT((COUNTIFS($O$2:O4,O4,$U$2:U4,U4)-1)/20)+1</f>
+      <c r="X4" s="25">
+        <f>INT((COUNTIFS($O$2:O4,O4,$V$2:V4,V4)-1)/20)+1</f>
         <v>0</v>
       </c>
-      <c r="X4" s="1" t="str">
-        <f t="shared" ref="X4:X7" si="1">V4 &amp; "-INC_" &amp; TEXT(W4,"00")</f>
+      <c r="Y4" s="1" t="str">
+        <f t="shared" ref="Y4:Y7" si="1">W4 &amp; "-INC_" &amp; TEXT(X4,"00")</f>
         <v>CHECK-INC_00</v>
       </c>
     </row>
-    <row r="5" spans="1:24" ht="16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" s="12"/>
       <c r="B5" s="12"/>
       <c r="C5" s="13"/>
@@ -1332,25 +1378,26 @@
       <c r="Q5" s="22"/>
       <c r="R5" s="16"/>
       <c r="S5" s="16"/>
-      <c r="T5" s="12"/>
-      <c r="U5" s="24" t="str">
+      <c r="T5" s="28"/>
+      <c r="U5" s="29"/>
+      <c r="V5" s="24" t="str">
         <f>"SL_" &amp; TEXT(INT((COUNTIF($O$2:O5,O5)-1)/100)+1,"00")</f>
         <v>SL_00</v>
       </c>
-      <c r="V5" s="25" t="str">
+      <c r="W5" s="25" t="str">
         <f>IF(COUNTIF($O$2:O5,O5)&gt;100,"CHECK",IF(COUNTIF($O$2:O5,O5)&lt;1,"CHECK","SL_"&amp;TEXT(INT((COUNTIF($O$2:O5,O5)-1)/100)+1,"00")))</f>
         <v>CHECK</v>
       </c>
-      <c r="W5" s="25">
-        <f>INT((COUNTIFS($O$2:O5,O5,$U$2:U5,U5)-1)/20)+1</f>
+      <c r="X5" s="25">
+        <f>INT((COUNTIFS($O$2:O5,O5,$V$2:V5,V5)-1)/20)+1</f>
         <v>0</v>
       </c>
-      <c r="X5" s="1" t="str">
+      <c r="Y5" s="1" t="str">
         <f t="shared" si="1"/>
         <v>CHECK-INC_00</v>
       </c>
     </row>
-    <row r="6" spans="1:24" ht="16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" s="12"/>
       <c r="B6" s="12"/>
       <c r="C6" s="13"/>
@@ -1370,25 +1417,26 @@
       <c r="Q6" s="22"/>
       <c r="R6" s="16"/>
       <c r="S6" s="16"/>
-      <c r="T6" s="12"/>
-      <c r="U6" s="24" t="str">
+      <c r="T6" s="28"/>
+      <c r="U6" s="29"/>
+      <c r="V6" s="24" t="str">
         <f>"SL_" &amp; TEXT(INT((COUNTIF($O$2:O6,O6)-1)/100)+1,"00")</f>
         <v>SL_00</v>
       </c>
-      <c r="V6" s="25" t="str">
+      <c r="W6" s="25" t="str">
         <f>IF(COUNTIF($O$2:O6,O6)&gt;100,"CHECK",IF(COUNTIF($O$2:O6,O6)&lt;1,"CHECK","SL_"&amp;TEXT(INT((COUNTIF($O$2:O6,O6)-1)/100)+1,"00")))</f>
         <v>CHECK</v>
       </c>
-      <c r="W6" s="25">
-        <f>INT((COUNTIFS($O$2:O6,O6,$U$2:U6,U6)-1)/20)+1</f>
+      <c r="X6" s="25">
+        <f>INT((COUNTIFS($O$2:O6,O6,$V$2:V6,V6)-1)/20)+1</f>
         <v>0</v>
       </c>
-      <c r="X6" s="1" t="str">
+      <c r="Y6" s="1" t="str">
         <f t="shared" si="1"/>
         <v>CHECK-INC_00</v>
       </c>
     </row>
-    <row r="7" spans="1:24" ht="16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="12"/>
       <c r="B7" s="12"/>
       <c r="C7" s="13"/>
@@ -1408,26 +1456,27 @@
       <c r="Q7" s="22"/>
       <c r="R7" s="16"/>
       <c r="S7" s="16"/>
-      <c r="T7" s="12"/>
-      <c r="U7" s="24" t="str">
+      <c r="T7" s="28"/>
+      <c r="U7" s="29"/>
+      <c r="V7" s="24" t="str">
         <f>"SL_" &amp; TEXT(INT((COUNTIF($O$2:O7,O7)-1)/100)+1,"00")</f>
         <v>SL_00</v>
       </c>
-      <c r="V7" s="25" t="str">
+      <c r="W7" s="25" t="str">
         <f>IF(COUNTIF($O$2:O7,O7)&gt;100,"CHECK",IF(COUNTIF($O$2:O7,O7)&lt;1,"CHECK","SL_"&amp;TEXT(INT((COUNTIF($O$2:O7,O7)-1)/100)+1,"00")))</f>
         <v>CHECK</v>
       </c>
-      <c r="W7" s="25">
-        <f>INT((COUNTIFS($O$2:O7,O7,$U$2:U7,U7)-1)/20)+1</f>
+      <c r="X7" s="25">
+        <f>INT((COUNTIFS($O$2:O7,O7,$V$2:V7,V7)-1)/20)+1</f>
         <v>0</v>
       </c>
-      <c r="X7" s="1" t="str">
+      <c r="Y7" s="1" t="str">
         <f t="shared" si="1"/>
         <v>CHECK-INC_00</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:X3" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:Y3" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/static/format-upload/KAWI-import-selling-barge.xlsx
+++ b/static/format-upload/KAWI-import-selling-barge.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10824"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11102"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/meinardus/Project/python/mines-project/backend/static/format-upload/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/meinardus/Project/python/mines-project/backend/staticfiles/format-upload/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2123B561-4FE5-DE43-9AA6-A765C5D32FFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79C58E3C-A622-A14E-BD19-D34A4965D187}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="880" windowWidth="36000" windowHeight="20100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -172,7 +172,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>Date Dumoning DT ke Braging / Tongkang</t>
+          <t>Date Dumping DT ke Barging / Tongkang</t>
         </r>
       </text>
     </comment>
@@ -282,7 +282,16 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">Kode LOT :
-KWL- (LIM)
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">KWL- (LIM)
 </t>
         </r>
         <r>
@@ -325,7 +334,57 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>HPAL / RKEF</t>
+          <t xml:space="preserve">Untuk HPAL (LIM) / RKEF (SAP).
+</t>
+        </r>
+        <r>
+          <rPr>
+            <u/>
+            <sz val="8"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Note : 
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Original LIM dijual atau di blending jadi SAP maka diadjust jadi </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>RKEF</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">. Sebaliknya SAP ke LIM mejadi </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>HPAL</t>
         </r>
       </text>
     </comment>
@@ -483,7 +542,7 @@
     <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yy;@"/>
     <numFmt numFmtId="166" formatCode="hh\.mm"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -538,6 +597,26 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="8"/>
+      <color rgb="FF000000"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="7">
@@ -687,7 +766,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -767,10 +846,7 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -1116,7 +1192,7 @@
     <col min="18" max="18" width="9" style="6" customWidth="1"/>
     <col min="19" max="19" width="12.5" style="6" customWidth="1"/>
     <col min="20" max="20" width="18.5" style="6" customWidth="1"/>
-    <col min="21" max="21" width="8.33203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.1640625" style="6" customWidth="1"/>
     <col min="22" max="22" width="12.1640625" style="6" customWidth="1"/>
     <col min="23" max="23" width="8.1640625" style="6" customWidth="1"/>
     <col min="24" max="24" width="12.1640625" style="6" customWidth="1"/>
@@ -1256,13 +1332,13 @@
         <f>X2</f>
         <v>1</v>
       </c>
-      <c r="S2" s="16" t="s">
+      <c r="S2" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="T2" s="12">
+      <c r="T2" s="28">
         <v>45873</v>
       </c>
-      <c r="U2" s="27"/>
+      <c r="U2" s="28"/>
       <c r="V2" s="24" t="str">
         <f>"SL_" &amp; TEXT(INT((COUNTIF($O$2:O2,O2)-1)/100)+1,"00")</f>
         <v>SL_01</v>
@@ -1299,9 +1375,9 @@
       <c r="P3" s="16"/>
       <c r="Q3" s="22"/>
       <c r="R3" s="16"/>
-      <c r="S3" s="16"/>
+      <c r="S3" s="27"/>
       <c r="T3" s="28"/>
-      <c r="U3" s="29"/>
+      <c r="U3" s="28"/>
       <c r="V3" s="24" t="str">
         <f>"SL_" &amp; TEXT(INT((COUNTIF($O$2:O3,O3)-1)/100)+1,"00")</f>
         <v>SL_00</v>
@@ -1338,9 +1414,9 @@
       <c r="P4" s="16"/>
       <c r="Q4" s="22"/>
       <c r="R4" s="16"/>
-      <c r="S4" s="16"/>
+      <c r="S4" s="27"/>
       <c r="T4" s="28"/>
-      <c r="U4" s="29"/>
+      <c r="U4" s="28"/>
       <c r="V4" s="24" t="str">
         <f>"SL_" &amp; TEXT(INT((COUNTIF($O$2:O4,O4)-1)/100)+1,"00")</f>
         <v>SL_00</v>
@@ -1377,9 +1453,9 @@
       <c r="P5" s="16"/>
       <c r="Q5" s="22"/>
       <c r="R5" s="16"/>
-      <c r="S5" s="16"/>
+      <c r="S5" s="27"/>
       <c r="T5" s="28"/>
-      <c r="U5" s="29"/>
+      <c r="U5" s="28"/>
       <c r="V5" s="24" t="str">
         <f>"SL_" &amp; TEXT(INT((COUNTIF($O$2:O5,O5)-1)/100)+1,"00")</f>
         <v>SL_00</v>
@@ -1416,9 +1492,9 @@
       <c r="P6" s="16"/>
       <c r="Q6" s="22"/>
       <c r="R6" s="16"/>
-      <c r="S6" s="16"/>
+      <c r="S6" s="27"/>
       <c r="T6" s="28"/>
-      <c r="U6" s="29"/>
+      <c r="U6" s="28"/>
       <c r="V6" s="24" t="str">
         <f>"SL_" &amp; TEXT(INT((COUNTIF($O$2:O6,O6)-1)/100)+1,"00")</f>
         <v>SL_00</v>
@@ -1455,9 +1531,9 @@
       <c r="P7" s="16"/>
       <c r="Q7" s="22"/>
       <c r="R7" s="16"/>
-      <c r="S7" s="16"/>
+      <c r="S7" s="27"/>
       <c r="T7" s="28"/>
-      <c r="U7" s="29"/>
+      <c r="U7" s="28"/>
       <c r="V7" s="24" t="str">
         <f>"SL_" &amp; TEXT(INT((COUNTIF($O$2:O7,O7)-1)/100)+1,"00")</f>
         <v>SL_00</v>
